--- a/numerical-workflows/v2/framework/经济/模块产销表/14_外循环_商店公会.xlsx
+++ b/numerical-workflows/v2/framework/经济/模块产销表/14_外循环_商店公会.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="产销阅读" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资源汇总" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="机器明细" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产销阅读" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源汇总" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机器明细" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'产销阅读'!$A$1:$J$133</definedName>
@@ -692,7 +692,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>公会周拍品掉落次数上限 合计x490；公会个人代币(15) 合计x525；公会集体代币(14) 合计x1050；贡献值 合计x1050；体力(3) 合计x480；金币(1) 合计x290000；专武经验高20000(110) 合计x10；角色抽卡券普通(106) 合计x5；角色经验高10000(102) 合计x14；专武抽卡券普通(107) 合计x4；另32项</t>
+          <t>公会周拍品掉落次数上限 16条；公会个人代币(15) 合计x525；公会集体代币(14) 合计x1050；贡献值 合计x1050；体力(3) 合计x480；金币(1) 合计x290000；专武经验高20000(110) 合计x10；角色抽卡券普通(106) 合计x5；角色经验高10000(102) 合计x14；专武抽卡券普通(107) 合计x4；另32项</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x20</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x20</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x20</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x20</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr"/>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x20</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x30</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x30</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr"/>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x30</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr"/>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x30</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr"/>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x30</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr"/>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x40</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x40</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr"/>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x40</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x40</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x40</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr"/>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>正式公会等级：公会周拍品掉落次数上限 x40</t>
+          <t>正式公会等级：公会周拍品掉落次数上限 x0</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr"/>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>映射装备商店：金色装备打孔器(1068) x1</t>
+          <t>映射装备商店：金色装备打孔器 x1</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>映射装备商店：紫色装备打孔器(1067) x1</t>
+          <t>映射装备商店：紫色装备打孔器 x1</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>映射装备商店：蓝色装备打孔器(1066) x1</t>
+          <t>映射装备商店：蓝色装备打孔器 x1</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>映射装备商店：红色装备打孔器(1069) x1</t>
+          <t>映射装备商店：红色装备打孔器 x1</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -7585,11 +7585,7 @@
           <t>紫色装备打孔器</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
+      <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
           <t>产出</t>
@@ -7635,11 +7631,7 @@
           <t>红色装备打孔器</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
+      <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
           <t>产出</t>
@@ -7685,11 +7677,7 @@
           <t>蓝色装备打孔器</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
+      <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="8" t="inlineStr">
         <is>
           <t>产出</t>
@@ -7785,11 +7773,7 @@
           <t>金色装备打孔器</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
+      <c r="C24" s="5" t="inlineStr"/>
       <c r="D24" s="8" t="inlineStr">
         <is>
           <t>产出</t>
@@ -23751,7 +23735,7 @@
         </is>
       </c>
       <c r="D294" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E294" s="5" t="inlineStr"/>
       <c r="F294" s="5" t="inlineStr"/>
@@ -23802,7 +23786,7 @@
         </is>
       </c>
       <c r="D295" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E295" s="5" t="inlineStr"/>
       <c r="F295" s="5" t="inlineStr"/>
@@ -23853,7 +23837,7 @@
         </is>
       </c>
       <c r="D296" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E296" s="5" t="inlineStr"/>
       <c r="F296" s="5" t="inlineStr"/>
@@ -23904,7 +23888,7 @@
         </is>
       </c>
       <c r="D297" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E297" s="5" t="inlineStr"/>
       <c r="F297" s="5" t="inlineStr"/>
@@ -23955,7 +23939,7 @@
         </is>
       </c>
       <c r="D298" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E298" s="5" t="inlineStr"/>
       <c r="F298" s="5" t="inlineStr"/>
@@ -24006,7 +23990,7 @@
         </is>
       </c>
       <c r="D299" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E299" s="5" t="inlineStr"/>
       <c r="F299" s="5" t="inlineStr"/>
@@ -24057,7 +24041,7 @@
         </is>
       </c>
       <c r="D300" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E300" s="5" t="inlineStr"/>
       <c r="F300" s="5" t="inlineStr"/>
@@ -24108,7 +24092,7 @@
         </is>
       </c>
       <c r="D301" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E301" s="5" t="inlineStr"/>
       <c r="F301" s="5" t="inlineStr"/>
@@ -24159,7 +24143,7 @@
         </is>
       </c>
       <c r="D302" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E302" s="5" t="inlineStr"/>
       <c r="F302" s="5" t="inlineStr"/>
@@ -24210,7 +24194,7 @@
         </is>
       </c>
       <c r="D303" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E303" s="5" t="inlineStr"/>
       <c r="F303" s="5" t="inlineStr"/>
@@ -24261,7 +24245,7 @@
         </is>
       </c>
       <c r="D304" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E304" s="5" t="inlineStr"/>
       <c r="F304" s="5" t="inlineStr"/>
@@ -24312,7 +24296,7 @@
         </is>
       </c>
       <c r="D305" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E305" s="5" t="inlineStr"/>
       <c r="F305" s="5" t="inlineStr"/>
@@ -24363,7 +24347,7 @@
         </is>
       </c>
       <c r="D306" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E306" s="5" t="inlineStr"/>
       <c r="F306" s="5" t="inlineStr"/>
@@ -24414,7 +24398,7 @@
         </is>
       </c>
       <c r="D307" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E307" s="5" t="inlineStr"/>
       <c r="F307" s="5" t="inlineStr"/>
@@ -24465,7 +24449,7 @@
         </is>
       </c>
       <c r="D308" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E308" s="5" t="inlineStr"/>
       <c r="F308" s="5" t="inlineStr"/>
@@ -24516,7 +24500,7 @@
         </is>
       </c>
       <c r="D309" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E309" s="5" t="inlineStr"/>
       <c r="F309" s="5" t="inlineStr"/>
